--- a/思达教育网站最终菜单栏-清晰版.xlsx
+++ b/思达教育网站最终菜单栏-清晰版.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\XiaoJuanSchoolPayment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC48D88-8A04-44CC-AE06-4FF94916C73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="最终菜单栏" sheetId="1" r:id="rId1"/>
@@ -20,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="421">
   <si>
     <t>思达教育网站最终菜单栏-清晰层级版</t>
   </si>
@@ -1289,19 +1293,16 @@
   </si>
   <si>
     <t>比把所有院校平铺在二级菜单更清楚</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1348,157 +1349,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1577,194 +1432,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1804,394 +1473,239 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFD1D5DB"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2202,7 +1716,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2230,154 +1744,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2526,3324 +1926,3410 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L116"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.38333333333333" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="9.38333333333333" customWidth="1"/>
+    <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="26.25" customWidth="1"/>
-    <col min="5" max="5" width="9.38333333333333" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="7" width="16.25" customWidth="1"/>
     <col min="8" max="8" width="11.25" customWidth="1"/>
     <col min="9" max="9" width="51.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="21" customHeight="1" spans="1:9">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:12" ht="21" customHeight="1">
+      <c r="A4" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" ht="14.4" spans="1:9">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.4" spans="1:9">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:12">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="H6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="14.4" spans="1:9">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="14.4" spans="1:9">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:12">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="14.4" spans="1:9">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" ht="14.4" spans="1:9">
-      <c r="A10" s="6" t="s">
+      <c r="J9" s="21" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" ht="14.4" spans="1:9">
-      <c r="A11" s="6" t="s">
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="14.4" spans="1:9">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:12">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" ht="14.4" spans="1:9">
-      <c r="A13" s="6" t="s">
+      <c r="H12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="6" t="s">
+      <c r="H13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" ht="14.4" spans="1:9">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:12">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" ht="14.4" spans="1:9">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" ht="14.4" spans="1:9">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:12">
+      <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="6" t="s">
+      <c r="H16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" ht="14.4" spans="1:9">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="6" t="s">
+      <c r="H17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" ht="14.4" spans="1:9">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="H18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" ht="14.4" spans="1:9">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="E19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" ht="14.4" spans="1:9">
-      <c r="A20" s="6" t="s">
+      <c r="H19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="E20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="H20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" ht="14.4" spans="1:9">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="E21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" ht="14.4" spans="1:9">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" ht="14.4" spans="1:9">
-      <c r="A23" s="6" t="s">
+      <c r="H22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" ht="14.4" spans="1:9">
-      <c r="A24" s="6" t="s">
+      <c r="H23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" ht="14.4" spans="1:9">
-      <c r="A25" s="6" t="s">
+      <c r="H24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" ht="14.4" spans="1:9">
-      <c r="A26" s="6" t="s">
+      <c r="H25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" ht="14.4" spans="1:9">
-      <c r="A27" s="6" t="s">
+      <c r="H26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" ht="14.4" spans="1:9">
-      <c r="A28" s="6" t="s">
+      <c r="H27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" ht="14.4" spans="1:9">
-      <c r="A29" s="6" t="s">
+      <c r="H28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1" spans="1:9">
-      <c r="A30" s="9" t="s">
+      <c r="H29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="21" customHeight="1">
+      <c r="A30" s="12" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="31" ht="14.4" spans="1:9">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G31" s="6" t="s">
+      <c r="E31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="6" t="s">
+      <c r="H31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" ht="14.4" spans="1:9">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="E32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="6" t="s">
+      <c r="H32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" ht="14.4" spans="1:9">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="6" t="s">
+      <c r="H33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" ht="14.4" spans="1:9">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="6" t="s">
+      <c r="H34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" ht="14.4" spans="1:9">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:9">
+      <c r="A35" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="H35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" ht="14.4" spans="1:9">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:9">
+      <c r="A36" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="6" t="s">
+      <c r="H36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="37" ht="14.4" spans="1:9">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:9">
+      <c r="A37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="E37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="14.4" spans="1:9">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:9">
+      <c r="A38" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="E38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="6" t="s">
+      <c r="H38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="39" ht="14.4" spans="1:9">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:9">
+      <c r="A39" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G39" s="6" t="s">
+      <c r="E39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="6" t="s">
+      <c r="H39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" ht="14.4" spans="1:9">
-      <c r="A40" s="6" t="s">
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="E40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="6" t="s">
+      <c r="H40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" ht="14.4" spans="1:9">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="6" t="s">
+      <c r="H41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="42" ht="14.4" spans="1:9">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="6" t="s">
+      <c r="H42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="43" ht="14.4" spans="1:9">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="6" t="s">
+      <c r="H43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="44" ht="14.4" spans="1:9">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="6" t="s">
+      <c r="H44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="45" ht="14.4" spans="1:9">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="46" ht="14.4" spans="1:9">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="E46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="6" t="s">
+      <c r="H46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="47" ht="14.4" spans="1:9">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G47" s="6" t="s">
+      <c r="E47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" s="6" t="s">
+      <c r="H47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="48" ht="14.4" spans="1:9">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="E48" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" s="6" t="s">
+      <c r="H48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="49" ht="14.4" spans="1:9">
-      <c r="A49" s="6" t="s">
+    <row r="49" spans="1:9">
+      <c r="A49" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="E49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="6" t="s">
+      <c r="H49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="50" ht="14.4" spans="1:9">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:9">
+      <c r="A50" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="E50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I50" s="6" t="s">
+      <c r="H50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="51" ht="14.4" spans="1:9">
-      <c r="A51" s="6" t="s">
+    <row r="51" spans="1:9">
+      <c r="A51" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G51" s="6" t="s">
+      <c r="E51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I51" s="6" t="s">
+      <c r="H51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="52" ht="14.4" spans="1:9">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:9">
+      <c r="A52" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="E52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I52" s="6" t="s">
+      <c r="H52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="53" ht="21" customHeight="1" spans="1:9">
-      <c r="A53" s="10" t="s">
+    <row r="53" spans="1:9" ht="21" customHeight="1">
+      <c r="A53" s="13" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="54" ht="14.4" spans="1:9">
-      <c r="A54" s="6" t="s">
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="E54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="H54" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" s="6" t="s">
+      <c r="H54" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="55" ht="14.4" spans="1:9">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:9">
+      <c r="A55" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G55" s="6" t="s">
+      <c r="E55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="H55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I55" s="6" t="s">
+      <c r="H55" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="56" ht="14.4" spans="1:9">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:9">
+      <c r="A56" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="E56" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="H56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I56" s="6" t="s">
+      <c r="H56" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="57" ht="14.4" spans="1:9">
-      <c r="A57" s="6" t="s">
+    <row r="57" spans="1:9">
+      <c r="A57" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G57" s="6" t="s">
+      <c r="E57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="H57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I57" s="6" t="s">
+      <c r="H57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="58" ht="14.4" spans="1:9">
-      <c r="A58" s="6" t="s">
+    <row r="58" spans="1:9">
+      <c r="A58" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="E58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="H58" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I58" s="6" t="s">
+      <c r="H58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="59" ht="14.4" spans="1:9">
-      <c r="A59" s="6" t="s">
+    <row r="59" spans="1:9">
+      <c r="A59" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G59" s="6" t="s">
+      <c r="E59" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I59" s="6" t="s">
+      <c r="H59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="60" ht="14.4" spans="1:9">
-      <c r="A60" s="6" t="s">
+    <row r="60" spans="1:9">
+      <c r="A60" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="E60" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="H60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I60" s="6" t="s">
+      <c r="H60" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="61" ht="14.4" spans="1:9">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:9">
+      <c r="A61" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G61" s="6" t="s">
+      <c r="E61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H61" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I61" s="6" t="s">
+      <c r="H61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="62" ht="21" customHeight="1" spans="1:9">
-      <c r="A62" s="11" t="s">
+    <row r="62" spans="1:9" ht="21" customHeight="1">
+      <c r="A62" s="14" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="63" ht="14.4" spans="1:9">
-      <c r="A63" s="6" t="s">
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63" s="6" t="s">
+      <c r="E63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" s="6" t="s">
+      <c r="H63" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="64" ht="14.4" spans="1:9">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:9">
+      <c r="A64" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="E64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I64" s="6" t="s">
+      <c r="H64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="65" ht="14.4" spans="1:9">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:9">
+      <c r="A65" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G65" s="6" t="s">
+      <c r="E65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I65" s="6" t="s">
+      <c r="H65" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="66" ht="14.4" spans="1:9">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:9">
+      <c r="A66" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="E66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I66" s="6" t="s">
+      <c r="H66" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="67" ht="14.4" spans="1:9">
-      <c r="A67" s="6" t="s">
+    <row r="67" spans="1:9">
+      <c r="A67" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G67" s="6" t="s">
+      <c r="E67" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I67" s="6" t="s">
+      <c r="H67" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="68" ht="14.4" spans="1:9">
-      <c r="A68" s="6" t="s">
+    <row r="68" spans="1:9">
+      <c r="A68" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="E68" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H68" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I68" s="6" t="s">
+      <c r="H68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="69" ht="14.4" spans="1:9">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:9">
+      <c r="A69" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G69" s="6" t="s">
+      <c r="E69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H69" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I69" s="6" t="s">
+      <c r="H69" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="70" ht="14.4" spans="1:9">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:9">
+      <c r="A70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G70" s="6" t="s">
+      <c r="E70" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H70" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I70" s="6" t="s">
+      <c r="H70" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="71" ht="14.4" spans="1:9">
-      <c r="A71" s="6" t="s">
+    <row r="71" spans="1:9">
+      <c r="A71" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G71" s="6" t="s">
+      <c r="E71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H71" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" s="6" t="s">
+      <c r="H71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="72" ht="14.4" spans="1:9">
-      <c r="A72" s="6" t="s">
+    <row r="72" spans="1:9">
+      <c r="A72" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="E72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="6" t="s">
+      <c r="H72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="73" ht="14.4" spans="1:9">
-      <c r="A73" s="6" t="s">
+    <row r="73" spans="1:9">
+      <c r="A73" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G73" s="6" t="s">
+      <c r="E73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="H73" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I73" s="6" t="s">
+      <c r="H73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="74" ht="21" customHeight="1" spans="1:9">
-      <c r="A74" s="12" t="s">
+    <row r="74" spans="1:9" ht="21" customHeight="1">
+      <c r="A74" s="15" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="75" ht="14.4" spans="1:9">
-      <c r="A75" s="6" t="s">
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G75" s="6" t="s">
+      <c r="E75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I75" s="6" t="s">
+      <c r="H75" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="76" ht="14.4" spans="1:9">
-      <c r="A76" s="6" t="s">
+    <row r="76" spans="1:9">
+      <c r="A76" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G76" s="6" t="s">
+      <c r="E76" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H76" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I76" s="6" t="s">
+      <c r="H76" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="77" ht="14.4" spans="1:9">
-      <c r="A77" s="6" t="s">
+    <row r="77" spans="1:9">
+      <c r="A77" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G77" s="6" t="s">
+      <c r="E77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I77" s="6" t="s">
+      <c r="H77" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="78" ht="14.4" spans="1:9">
-      <c r="A78" s="6" t="s">
+    <row r="78" spans="1:9">
+      <c r="A78" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="E78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H78" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I78" s="6" t="s">
+      <c r="H78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="79" ht="14.4" spans="1:9">
-      <c r="A79" s="6" t="s">
+    <row r="79" spans="1:9">
+      <c r="A79" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G79" s="6" t="s">
+      <c r="E79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H79" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I79" s="6" t="s">
+      <c r="H79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="80" ht="14.4" spans="1:9">
-      <c r="A80" s="6" t="s">
+    <row r="80" spans="1:9">
+      <c r="A80" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G80" s="6" t="s">
+      <c r="E80" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H80" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I80" s="6" t="s">
+      <c r="H80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="81" ht="14.4" spans="1:9">
-      <c r="A81" s="6" t="s">
+    <row r="81" spans="1:9">
+      <c r="A81" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G81" s="6" t="s">
+      <c r="E81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H81" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I81" s="6" t="s">
+      <c r="H81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="82" ht="14.4" spans="1:9">
-      <c r="A82" s="6" t="s">
+    <row r="82" spans="1:9">
+      <c r="A82" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G82" s="6" t="s">
+      <c r="E82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H82" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" s="6" t="s">
+      <c r="H82" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="83" ht="14.4" spans="1:9">
-      <c r="A83" s="6" t="s">
+    <row r="83" spans="1:9">
+      <c r="A83" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G83" s="6" t="s">
+      <c r="E83" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I83" s="6" t="s">
+      <c r="H83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="84" ht="14.4" spans="1:9">
-      <c r="A84" s="6" t="s">
+    <row r="84" spans="1:9">
+      <c r="A84" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G84" s="6" t="s">
+      <c r="E84" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I84" s="6" t="s">
+      <c r="H84" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="85" ht="14.4" spans="1:9">
-      <c r="A85" s="6" t="s">
+    <row r="85" spans="1:9">
+      <c r="A85" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G85" s="6" t="s">
+      <c r="E85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" s="6" t="s">
+      <c r="H85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="86" ht="14.4" spans="1:9">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:9">
+      <c r="A86" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G86" s="6" t="s">
+      <c r="E86" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H86" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I86" s="6" t="s">
+      <c r="H86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="87" ht="21" customHeight="1" spans="1:9">
-      <c r="A87" s="14" t="s">
+    <row r="87" spans="1:9" ht="21" customHeight="1">
+      <c r="A87" s="16" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="88" ht="14.4" spans="1:9">
-      <c r="A88" s="6" t="s">
+      <c r="B87" s="10"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="E88" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H88" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I88" s="6" t="s">
+      <c r="H88" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="89" ht="14.4" spans="1:9">
-      <c r="A89" s="6" t="s">
+    <row r="89" spans="1:9">
+      <c r="A89" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G89" s="6" t="s">
+      <c r="E89" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H89" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I89" s="6" t="s">
+      <c r="H89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="90" ht="14.4" spans="1:9">
-      <c r="A90" s="6" t="s">
+    <row r="90" spans="1:9">
+      <c r="A90" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G90" s="6" t="s">
+      <c r="E90" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H90" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I90" s="6" t="s">
+      <c r="H90" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" s="4" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="91" ht="14.4" spans="1:9">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:9">
+      <c r="A91" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G91" s="6" t="s">
+      <c r="E91" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H91" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I91" s="6" t="s">
+      <c r="H91" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="92" ht="14.4" spans="1:9">
-      <c r="A92" s="6" t="s">
+    <row r="92" spans="1:9">
+      <c r="A92" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="E92" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" ht="14.4" spans="1:9">
-      <c r="A93" s="6" t="s">
+      <c r="H92" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G93" s="6" t="s">
+      <c r="E93" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H93" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="94" ht="14.4" spans="1:9">
-      <c r="A94" s="6" t="s">
+      <c r="H93" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="E94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H94" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="95" ht="14.4" spans="1:9">
-      <c r="A95" s="6" t="s">
+      <c r="H94" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G95" s="6" t="s">
+      <c r="E95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H95" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" ht="14.4" spans="1:9">
-      <c r="A96" s="6" t="s">
+      <c r="H95" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G96" s="6" t="s">
+      <c r="E96" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H96" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I96" s="6" t="s">
+      <c r="H96" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="97" ht="14.4" spans="1:9">
-      <c r="A97" s="6" t="s">
+    <row r="97" spans="1:9">
+      <c r="A97" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G97" s="6" t="s">
+      <c r="E97" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H97" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="98" ht="14.4" spans="1:9">
-      <c r="A98" s="6" t="s">
+      <c r="H97" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98" s="6" t="s">
+      <c r="E98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H98" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" ht="14.4" spans="1:9">
-      <c r="A99" s="6" t="s">
+      <c r="H98" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G99" s="6" t="s">
+      <c r="E99" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H99" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="100" ht="21" customHeight="1" spans="1:9">
-      <c r="A100" s="15" t="s">
+      <c r="H99" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="21" customHeight="1">
+      <c r="A100" s="17" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="101" ht="14.4" spans="1:9">
-      <c r="A101" s="6" t="s">
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="10"/>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G101" s="6" t="s">
+      <c r="E101" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H101" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I101" s="6" t="s">
+      <c r="H101" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" s="4" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="102" ht="14.4" spans="1:9">
-      <c r="A102" s="6" t="s">
+    <row r="102" spans="1:9">
+      <c r="A102" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G102" s="6" t="s">
+      <c r="E102" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H102" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I102" s="6" t="s">
+      <c r="H102" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="4" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="103" ht="14.4" spans="1:9">
-      <c r="A103" s="6" t="s">
+    <row r="103" spans="1:9">
+      <c r="A103" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G103" s="6" t="s">
+      <c r="E103" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G103" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H103" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I103" s="6" t="s">
+      <c r="H103" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="104" ht="14.4" spans="1:9">
-      <c r="A104" s="6" t="s">
+    <row r="104" spans="1:9">
+      <c r="A104" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E104" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G104" s="6" t="s">
+      <c r="E104" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H104" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I104" s="6" t="s">
+      <c r="H104" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="105" ht="14.4" spans="1:9">
-      <c r="A105" s="6" t="s">
+    <row r="105" spans="1:9">
+      <c r="A105" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G105" s="6" t="s">
+      <c r="E105" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H105" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I105" s="6" t="s">
+      <c r="H105" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" s="4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="106" ht="14.4" spans="1:9">
-      <c r="A106" s="6" t="s">
+    <row r="106" spans="1:9">
+      <c r="A106" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G106" s="6" t="s">
+      <c r="E106" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H106" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I106" s="6" t="s">
+      <c r="H106" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" s="4" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="107" ht="14.4" spans="1:9">
-      <c r="A107" s="6" t="s">
+    <row r="107" spans="1:9">
+      <c r="A107" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G107" s="6" t="s">
+      <c r="E107" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H107" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I107" s="6" t="s">
+      <c r="H107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" s="4" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="108" ht="21" customHeight="1" spans="1:9">
-      <c r="A108" s="16" t="s">
+    <row r="108" spans="1:9" ht="21" customHeight="1">
+      <c r="A108" s="18" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="109" ht="14.4" spans="1:9">
-      <c r="A109" s="6" t="s">
+      <c r="B108" s="10"/>
+      <c r="C108" s="10"/>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="10"/>
+      <c r="H108" s="10"/>
+      <c r="I108" s="10"/>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G109" s="6" t="s">
+      <c r="E109" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G109" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H109" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I109" s="6" t="s">
+      <c r="H109" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" s="4" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="110" ht="14.4" spans="1:9">
-      <c r="A110" s="6" t="s">
+    <row r="110" spans="1:9">
+      <c r="A110" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E110" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G110" s="6" t="s">
+      <c r="E110" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G110" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H110" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I110" s="6" t="s">
+      <c r="H110" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="111" ht="14.4" spans="1:9">
-      <c r="A111" s="6" t="s">
+    <row r="111" spans="1:9">
+      <c r="A111" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G111" s="6" t="s">
+      <c r="E111" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H111" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I111" s="6" t="s">
+      <c r="H111" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" s="4" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="112" ht="14.4" spans="1:9">
-      <c r="A112" s="6" t="s">
+    <row r="112" spans="1:9">
+      <c r="A112" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="E112" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G112" s="6" t="s">
+      <c r="E112" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="H112" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I112" s="6" t="s">
+      <c r="H112" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" s="4" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="113" ht="14.4" spans="1:9">
-      <c r="A113" s="6" t="s">
+    <row r="113" spans="1:9">
+      <c r="A113" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="E113" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G113" s="6" t="s">
+      <c r="E113" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="H113" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I113" s="6" t="s">
+      <c r="H113" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" s="4" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="114" ht="14.4" spans="1:9">
-      <c r="A114" s="6" t="s">
+    <row r="114" spans="1:9">
+      <c r="A114" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="E114" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G114" s="6" t="s">
+      <c r="E114" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H114" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="115" ht="21" customHeight="1" spans="1:9">
-      <c r="A115" s="17" t="s">
+      <c r="H114" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="21" customHeight="1">
+      <c r="A115" s="19" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="116" ht="14.4" spans="1:9">
-      <c r="A116" s="6" t="s">
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="10"/>
+      <c r="H115" s="10"/>
+      <c r="I115" s="10"/>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G116" s="6" t="s">
+      <c r="E116" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="H116" s="18" t="s">
+      <c r="H116" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="I116" s="6" t="s">
+      <c r="I116" s="4" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A115:I115"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A108:I108"/>
-    <mergeCell ref="A115:I115"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.13333333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.125" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
     <col min="3" max="3" width="32.5" customWidth="1"/>
     <col min="4" max="4" width="16.25" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="3" ht="14.4" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="14.4" spans="1:5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="5" ht="14.4" spans="1:5">
-      <c r="A5" s="3">
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="6" ht="14.4" spans="1:5">
-      <c r="A6" s="3">
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="7" ht="14.4" spans="1:5">
-      <c r="A7" s="3">
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="8" ht="14.4" spans="1:5">
-      <c r="A8" s="3">
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="9" ht="14.4" spans="1:5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="10" ht="14.4" spans="1:5">
-      <c r="A10" s="3">
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="11" ht="14.4" spans="1:5">
-      <c r="A11" s="3">
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="12" ht="14.4" spans="1:5">
-      <c r="A12" s="3">
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5852,15 +5338,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -5868,120 +5352,123 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="3" ht="14.4" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="27">
+      <c r="A4" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4" ht="27">
+      <c r="A5" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="6" ht="14.4" spans="1:4">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4" ht="27">
+      <c r="A6" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="7" ht="14.4" spans="1:4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="8" ht="14.4" spans="1:4">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="9" ht="14.4" spans="1:4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="10" ht="14.4" spans="1:4">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>402</v>
       </c>
     </row>
@@ -5990,6 +5477,5 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/思达教育网站最终菜单栏-清晰版.xlsx
+++ b/思达教育网站最终菜单栏-清晰版.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC48D88-8A04-44CC-AE06-4FF94916C73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="最终菜单栏" sheetId="1" r:id="rId1"/>
@@ -1515,25 +1515,16 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1546,11 +1537,20 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1947,17 +1947,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
@@ -1989,17 +1989,17 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="4" t="s">
@@ -2145,7 +2145,7 @@
       <c r="I9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="10" t="s">
         <v>420</v>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       <c r="I10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="20"/>
+      <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="4" t="s">
@@ -2731,17 +2731,17 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
@@ -3382,17 +3382,17 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="21" customHeight="1">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
@@ -3627,17 +3627,17 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="21" customHeight="1">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="4" t="s">
@@ -3959,17 +3959,17 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="21" customHeight="1">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="4" t="s">
@@ -4320,17 +4320,17 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="21" customHeight="1">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="4" t="s">
@@ -4681,17 +4681,17 @@
       </c>
     </row>
     <row r="100" spans="1:9" ht="21" customHeight="1">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="4" t="s">
@@ -4897,17 +4897,17 @@
       </c>
     </row>
     <row r="108" spans="1:9" ht="21" customHeight="1">
-      <c r="A108" s="18" t="s">
+      <c r="A108" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="4" t="s">
@@ -5084,17 +5084,17 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="21" customHeight="1">
-      <c r="A115" s="19" t="s">
+      <c r="A115" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="10"/>
-      <c r="H115" s="10"/>
-      <c r="I115" s="10"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="12"/>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="4" t="s">
@@ -5127,16 +5127,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A74:I74"/>
     <mergeCell ref="A87:I87"/>
     <mergeCell ref="A100:I100"/>
     <mergeCell ref="A108:I108"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A62:I62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5155,13 +5155,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
@@ -5353,12 +5353,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
